--- a/data/availability/projects/city-edge-developments/mazarine-apartments-new-alamein.xlsx
+++ b/data/availability/projects/city-edge-developments/mazarine-apartments-new-alamein.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mazarine-apartments-new-alamein</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1009,7 +1019,6 @@
       <c r="G2" t="n">
         <v>140</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1020,7 +1029,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1066,7 +1075,6 @@
       <c r="G3" t="n">
         <v>231</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1077,7 +1085,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1123,7 +1131,6 @@
       <c r="G4" t="n">
         <v>258</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1134,7 +1141,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1195,7 +1202,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1241,7 +1248,6 @@
       <c r="G6" t="n">
         <v>235</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1252,7 +1258,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,7 +1304,6 @@
       <c r="G7" t="n">
         <v>252</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1309,7 +1314,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1370,7 +1375,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1416,7 +1421,6 @@
       <c r="G9" t="n">
         <v>237</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1427,7 +1431,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1473,7 +1477,6 @@
       <c r="G10" t="n">
         <v>249</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1484,7 +1487,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1530,7 +1533,6 @@
       <c r="G11" t="n">
         <v>207</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1541,7 +1543,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1587,7 +1589,6 @@
       <c r="G12" t="n">
         <v>216</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1598,7 +1599,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1644,7 +1645,6 @@
       <c r="G13" t="n">
         <v>257</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1701,7 +1701,6 @@
       <c r="G14" t="n">
         <v>451</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Sea / Panoramic View</t>
@@ -1712,7 +1711,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
